--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:40:33+00:00</t>
+    <t>2026-07-21T12:38:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Bundle</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Bundle|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -843,7 +843,7 @@
     <t>Bundle.entry:DocumentReference.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-document-reference}
+    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-document-reference|3.0.1}
 </t>
   </si>
   <si>
@@ -962,7 +962,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient}
+    <t xml:space="preserve">Patient {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1}
 </t>
   </si>
   <si>
@@ -1075,7 +1075,7 @@
     <t>Bundle.entry:Practitioner.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner}
+    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.0.1}
 </t>
   </si>
   <si>
@@ -1184,7 +1184,7 @@
     <t>Bundle.entry:PractitionerRole.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole}
+    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.0.1}
 </t>
   </si>
   <si>
@@ -1293,7 +1293,7 @@
     <t>Bundle.entry:Organization.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization}
+    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.0.1}
 </t>
   </si>
   <si>
@@ -1402,7 +1402,7 @@
     <t>Bundle.entry:RelatedPerson.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person}
+    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.0.1}
 </t>
   </si>
   <si>
@@ -1670,7 +1670,7 @@
     <t>Profil de la ressource DocumentReference pour le cahier de liaison. Il regroupe les informations relatives à la note.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DocumentReference</t>
+    <t>http://hl7.org/fhir/StructureDefinition/DocumentReference|4.0.1</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -1753,7 +1753,7 @@
     <t>isEmergency</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-ext-is-emergency}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-ext-is-emergency|3.0.1}
 </t>
   </si>
   <si>
@@ -1857,7 +1857,7 @@
     <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J23-TypeNoteCahierLiaison-CISIS/FHIR/JDV-J23-TypeNoteCahierLiaison-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J23-TypeNoteCahierLiaison-CISIS/FHIR/JDV-J23-TypeNoteCahierLiaison-CISIS|20200424120000</t>
   </si>
   <si>
     <t>DocumentReference.category</t>
@@ -1888,7 +1888,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1)
 </t>
   </si>
   <si>
@@ -1917,7 +1917,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.0.1|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.0.1|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.0.1)
 </t>
   </si>
   <si>
@@ -2045,7 +2045,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS|20200424120000</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -2321,7 +2321,7 @@
     <t>This list of codes represents the main clinical acts being documented.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|3.0.0</t>
   </si>
   <si>
     <t>DocumentReference.context.period</t>
@@ -2414,7 +2414,7 @@
     <t>complex-type</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Context</t>
@@ -3445,7 +3445,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="144.1953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="94.22265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="108.75390625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:38:43+00:00</t>
+    <t>2026-07-21T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:31+00:00</t>
+    <t>2026-07-21T13:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:21:42+00:00</t>
+    <t>2026-07-21T13:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
